--- a/scenarios/S06_vlb_ico_marketing/deliverables/채널전략_일정_시트.xlsx
+++ b/scenarios/S06_vlb_ico_marketing/deliverables/채널전략_일정_시트.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="채널전략" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="토큰배분" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -796,7 +797,6 @@
           <t>12개월 클리프+24개월</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -812,7 +812,6 @@
           <t>12개월 클리프+12개월</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -848,7 +847,6 @@
           <t>6개월 베스팅</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -864,7 +862,6 @@
           <t>3개월 베스팅</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -880,7 +877,6 @@
           <t>없음</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -896,7 +892,372 @@
           <t>36개월 분할</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>req_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>일시</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>요청자</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>소스</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>결정</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>영향 산출물</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>변경유형</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>DA점수</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>위키 커밋</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REQ-20250308-RU-ETH-VLB-ICO-PLAN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:38:54.789+09:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>마케팅 리드</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bench:S06:B00000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>조건부 승인: 관할권, 토큰 법적 분류, 제재·KYC/AML·개인정보 처리, 교차 모듈 승인 및 판매 중지 기준을 확정하고 법률·컴플라이언스 승인 전에는 외부 마케팅과 토큰 세일 공지를 진행하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>러시아 ETH 기반 VLB ICO 실행계획에 백서 배포, KYC 안내, 토큰 세일 일정 커뮤니케이션을 포함하는 작업을 착수하며 규제 검토가 필요합니다.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ICO 마케팅 실행계획, 백서 배포 계획, KYC 절차 안내, 토큰 세일 일정 커뮤니케이션 계획</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/b55a28a68d86bb7c5173f72c8bc94767ebcf1397</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-20250308-RU-ETH-VLB-ICO-EXECUTION-RESULT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:56:48.516+09:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>마케팅 리드</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bench:S06:B00001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7개 영향 산출물의 변경을 승인·반영한 실행 결과로 기록하되, 법률·컴플라이언스·보안 승인과 증적 확보 전 백서 공개·투자자 모집·토큰 세일 일정 공지 등 외부 커뮤니케이션은 보류한다.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>러시아 ETH 기반 VLB ICO 실행계획에 마케팅, 백서 배포, KYC/AML, 토큰 세일 공지, 규제 검토 및 외부 커뮤니케이션 보류 게이트를 반영</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ICO 마케팅 실행계획; 백서 배포 계획; KYC/AML 절차 안내; 토큰 세일 일정 커뮤니케이션 계획; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/939370cc457c7c98593155296d2da29bbddec580</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-20250308-RU-ETH-VLB-ICO-APPROVAL-PAYLOAD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:53:22.264+09:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>마케팅 리드</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bench:S06:B00010</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>관련 산출물과 LLM Wiki 갱신을 승인한다. 단, 토큰 법적 분류·허용 관할권·제재 제한·KYC/AML 및 개인정보 처리·스마트컨트랙트 보안·공식 채널 통제에 대한 승인과 증적이 확보될 때까지 백서 공개, 투자자 모집, 토큰 세일 일정 공지 및 기타 외부 커뮤니케이션은 보류한다.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>러시아 ETH 기반 VLB ICO 마케팅 실행계획과 백서·KYC·토큰 세일 커뮤니케이션 범위를 반영하되 승인과 증적 확보 전 외부 공개를 보류한다.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ICO 마케팅 실행계획, 백서 배포 계획, KYC 절차 안내, 토큰 세일 일정 커뮤니케이션 계획, 산출물_설계서.docx, 요구사항_추적표.xlsx, 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/5db3dfe32bfc54e9f73bd3aa91a4c8b41193f43c</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-20250308-RU-ETH-VLB-ICO-APPROVAL-UPDATE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:49:46.976+09:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>마케팅 리드</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bench:S06:B00100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>점수상 진행 가능으로 승인하되, 관할권별 법률 승인·개인정보 및 AML 통제·결제와 환불·문서 단일 기준본·사고 대응 증적이 확보되기 전까지 백서 공개, 투자자 모집, 토큰 세일 일정 공지 및 기타 외부 커뮤니케이션을 보류한다.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>러시아 및 ETH 대상 마케팅, 백서 배포, KYC/AML, 토큰 세일 일정 공지와 법률·컴플라이언스·보안·운영 승인 게이트를 추가한다.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ICO 마케팅 실행계획, 백서 배포 계획, KYC 절차 안내, 토큰 세일 일정 커뮤니케이션 계획, 산출물_설계서.docx, 요구사항_추적표.xlsx, 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>add+modify</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/94d8a36773c828cc64b2884f5c6a8683d31b4f4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-20250308-RU-ETH-VLB-ICO-APPROVAL-EVIDENCE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:46:25.967+09:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>마케팅 리드</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bench:S06:B01000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7개 영향 산출물의 변경사항 반영을 조건부 승인하고 기록한다. 법률·컴플라이언스·보안·운영 승인 증적과 핵심 통제가 확정되기 전 백서 공개, 투자자 모집, 토큰 세일 일정 공지 및 기타 외부 커뮤니케이션은 보류한다.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>러시아·ETH 대상 마케팅, 백서 배포, KYC/AML, 세일 일정 커뮤니케이션, 규제·보안 승인 게이트와 외부 공개 보류 통제를 반영한다.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ICO 마케팅 실행계획, 백서 배포 계획, KYC 절차 안내, 토큰 세일 일정 커뮤니케이션 계획, 산출물_설계서.docx, 요구사항_추적표.xlsx, 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/c0b177db23033bce42c6c54b0a8a19746b7409e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-20250308-RU-ETH-VLB-ICO-EXECUTION</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-31T23:42:24.113+09:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>마케팅 리드</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bench:S06:B10000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>조건부 승인에 따라 7개 산출물의 변경사항을 반영한 것으로 보고하되, 관할권별 법률 승인·개인정보 및 제재 통제·스마트컨트랙트와 환불 운영·사고대응 증적 확보 전 외부 공개는 보류한다.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>러시아 및 ETH 기반 VLB ICO의 마케팅·백서 배포·KYC/AML·토큰 세일 일정 커뮤니케이션과 규제·보안 선행조건을 반영한다.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ICO 마케팅 실행계획, 백서 배포 계획, KYC 절차 안내, 토큰 세일 일정 커뮤니케이션 계획, 산출물_설계서.docx, 요구사항_추적표.xlsx, 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>modify</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/e20bb91de9e0dfaf25973bbbbe4667ba9dd891df</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
